--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דניאלה גולדפיין – Like a Swing</v>
+        <v>אסתר שמיר ויהל דורון – בצד השני של הפחד</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c%d7%94-%d7%92%d7%95%d7%9c%d7%93%d7%a4%d7%99%d7%99%d7%9f-like-a-swing/</v>
+        <v>https://yosmusic.com/%d7%90%d7%a1%d7%aa%d7%a8-%d7%a9%d7%9e%d7%99%d7%a8-%d7%95%d7%99%d7%94%d7%9c-%d7%93%d7%95%d7%a8%d7%95%d7%9f-%d7%91%d7%a6%d7%93-%d7%94%d7%a9%d7%a0%d7%99-%d7%a9%d7%9c-%d7%94%d7%a4%d7%97%d7%93/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “Like a Swing” של דניאלה גולדפיין נוגע ומגיע מתוך הפשטות שלו. אין כאן ניסיון להרשים בהפקה גדולה, מהלכים דרמטיים או כתיבה מתוחכמת מדי, אלא יצירה קטנה, אינטימית וכמעט חשופה, שנשמעת כמו מכתב אישי שהולחן ברגע שקט באמצע הלילה. הרעיון</v>
+        <v>שיתוף הפעולה בין אסתר שמיר ליהל דורון ב״בצד השני של הפחד״ הוא לא רק דואט מוזיקלי  אלא מפגש בין שתי תפיסות של רגש, כתיבה ונחמה במוזיקה הישראלית. מצד אחד קול שנושא איתו היסטוריה תרבותית שלמה, ומצד שני יוצר עכשווי שמביא</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דניאלה גולדפיין – Like a Swing</v>
+        <v>אסתר שמיר ויהל דורון – בצד השני של הפחד</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אסתר שמיר ויהל דורון – בצד השני של הפחד</v>
+        <v>יובל קונסטנטיני - שירי אהבה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a1%d7%aa%d7%a8-%d7%a9%d7%9e%d7%99%d7%a8-%d7%95%d7%99%d7%94%d7%9c-%d7%93%d7%95%d7%a8%d7%95%d7%9f-%d7%91%d7%a6%d7%93-%d7%94%d7%a9%d7%a0%d7%99-%d7%a9%d7%9c-%d7%94%d7%a4%d7%97%d7%93/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410999&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>שיתוף הפעולה בין אסתר שמיר ליהל דורון ב״בצד השני של הפחד״ הוא לא רק דואט מוזיקלי  אלא מפגש בין שתי תפיסות של רגש, כתיבה ונחמה במוזיקה הישראלית. מצד אחד קול שנושא איתו היסטוריה תרבותית שלמה, ומצד שני יוצר עכשווי שמביא</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,316 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אסתר שמיר ויהל דורון – בצד השני של הפחד</v>
+        <v>יובל קונסטנטיני - שירי אהבה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>יובל גולד &amp; שירה זלוף - מחר יבוא מחר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410998&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>יובל גולד &amp; שירה זלוף - מחר יבוא מחר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>טלי רבקה סימן טוב - יוצאת לדרך</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410997&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>טלי רבקה סימן טוב - יוצאת לדרך</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>טודיאל - לא ממלא לי ת'נשמה</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410996&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>טודיאל - לא ממלא לי ת'נשמה</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>זיו גבאי - מין נהאר לי נפטר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410995&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>זיו גבאי - מין נהאר לי נפטר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>דקלה תפילין - צלקת שלך על הלב</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410994&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>דקלה תפילין - צלקת שלך על הלב</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>בני קראוס - ממשיך לחיות</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410993&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>בני קראוס - ממשיך לחיות</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אליאור נונה - מחרוזת מאמי שלי 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410992&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אליאור נונה - מחרוזת מאמי שלי 2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>איציק שריקי - בָּבָּא לִּיווִי</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410991&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>איציק שריקי - בָּבָּא לִּיווִי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל קונסטנטיני - שירי אהבה</v>
+        <v>אביגייל רוז – רגעים של שפיות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410999&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%99%d7%92%d7%99%d7%99%d7%9c-%d7%a8%d7%95%d7%96-%d7%a8%d7%92%d7%a2%d7%99%d7%9d-%d7%a9%d7%9c-%d7%a9%d7%a4%d7%99%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>אביגייל רוז בונה ב״רגעים של שפיות״ בלדה שנעה בין אינטימיות כמעט לוחשת לבין התפרצות רגשית דרמטית. הטקסט, ההלחנה והעיבוד עובדים יחד כדי לתאר תהליך נפשי: ניסיון להחזיק את החיים בשליטה – ואז רגע של קריסה, או אולי שחרור. השיר נפתח</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,316 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל קונסטנטיני - שירי אהבה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>יובל גולד &amp; שירה זלוף - מחר יבוא מחר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410998&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>יובל גולד &amp; שירה זלוף - מחר יבוא מחר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>טלי רבקה סימן טוב - יוצאת לדרך</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410997&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>טלי רבקה סימן טוב - יוצאת לדרך</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>טודיאל - לא ממלא לי ת'נשמה</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410996&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>טודיאל - לא ממלא לי ת'נשמה</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>זיו גבאי - מין נהאר לי נפטר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410995&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>זיו גבאי - מין נהאר לי נפטר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>דקלה תפילין - צלקת שלך על הלב</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410994&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>דקלה תפילין - צלקת שלך על הלב</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>בני קראוס - ממשיך לחיות</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410993&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>בני קראוס - ממשיך לחיות</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אליאור נונה - מחרוזת מאמי שלי 2026</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410992&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אליאור נונה - מחרוזת מאמי שלי 2026</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>איציק שריקי - בָּבָּא לִּיווִי</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410991&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>איציק שריקי - בָּבָּא לִּיווִי</v>
+        <v>אביגייל רוז – רגעים של שפיות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אביגייל רוז – רגעים של שפיות</v>
+        <v>ליאב דהן - נלחמתי עלייך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%99%d7%92%d7%99%d7%99%d7%9c-%d7%a8%d7%95%d7%96-%d7%a8%d7%92%d7%a2%d7%99%d7%9d-%d7%a9%d7%9c-%d7%a9%d7%a4%d7%99%d7%95%d7%aa/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411006&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-24</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אביגייל רוז בונה ב״רגעים של שפיות״ בלדה שנעה בין אינטימיות כמעט לוחשת לבין התפרצות רגשית דרמטית. הטקסט, ההלחנה והעיבוד עובדים יחד כדי לתאר תהליך נפשי: ניסיון להחזיק את החיים בשליטה – ואז רגע של קריסה, או אולי שחרור. השיר נפתח</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אביגייל רוז – רגעים של שפיות</v>
+        <v>ליאב דהן - נלחמתי עלייך</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ישראל בן חמו - נרדי נתן ריחו</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411005&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>ישראל בן חמו - נרדי נתן ריחו</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ישי מדר - להתקרב אליך</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411004&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>ישי מדר - להתקרב אליך</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>יקיר לנקרי - הלב שלי ז״ל</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411003&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>יקיר לנקרי - הלב שלי ז״ל</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>יניב בן משיח - בית חם</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411002&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>יניב בן משיח - בית חם</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יניב איזנקוט - נשבעתי לך ילדה 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411001&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יניב איזנקוט - נשבעתי לך ילדה 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אלכס - בא אלייך</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411000&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אלכס - בא אלייך</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>נתלי – באמא שך</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="C9" t="str">
+        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%9c%d7%99-%d7%91%d7%90%d7%9e%d7%90-%d7%a9%d7%9a/</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>נתלי צפר ב״באמא שך״ יוצרת שיר פרידה כועס, עייף ופגיע בו־זמנית – כזה שמסתיר כאב עמוק מאחורי שפה יומיומית, כמעט רחובית. הכוח של השיר נמצא בדיוק בפער הזה: בין הקצב הריקודי והעיבוד הלטיני־ים־תיכוני לבין הטקסט שמתאר מערכת יחסים רעילה, מתישה</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>נתלי – באמא שך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליאב דהן - נלחמתי עלייך</v>
+        <v>שיר אוחנה - המילים שרציתי לכתוב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411006&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411012&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-24</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליאב דהן - נלחמתי עלייך</v>
+        <v>שיר אוחנה - המילים שרציתי לכתוב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ישראל בן חמו - נרדי נתן ריחו</v>
+        <v>שי אוחיון - אלקנה</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411005&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411011&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-24</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ישראל בן חמו - נרדי נתן ריחו</v>
+        <v>שי אוחיון - אלקנה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ישי מדר - להתקרב אליך</v>
+        <v>קורל - בלילות</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411004&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411010&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-24</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ישי מדר - להתקרב אליך</v>
+        <v>קורל - בלילות</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יקיר לנקרי - הלב שלי ז״ל</v>
+        <v>נתנאל פורטל - כפרה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411003&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411009&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-24</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יקיר לנקרי - הלב שלי ז״ל</v>
+        <v>נתנאל פורטל - כפרה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יניב בן משיח - בית חם</v>
+        <v>מוטי אוריאל - עם סגולה</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411002&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411008&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-24</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יניב בן משיח - בית חם</v>
+        <v>מוטי אוריאל - עם סגולה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יניב איזנקוט - נשבעתי לך ילדה 2026</v>
+        <v>ליאל שרעבי - לא סופרת</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411001&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411007&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-24</v>
@@ -659,88 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יניב איזנקוט - נשבעתי לך ילדה 2026</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אלכס - בא אלייך</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411000&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אלכס - בא אלייך</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>נתלי – באמא שך</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="C9" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%9c%d7%99-%d7%91%d7%90%d7%9e%d7%90-%d7%a9%d7%9a/</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v>נתלי צפר ב״באמא שך״ יוצרת שיר פרידה כועס, עייף ופגיע בו־זמנית – כזה שמסתיר כאב עמוק מאחורי שפה יומיומית, כמעט רחובית. הכוח של השיר נמצא בדיוק בפער הזה: בין הקצב הריקודי והעיבוד הלטיני־ים־תיכוני לבין הטקסט שמתאר מערכת יחסים רעילה, מתישה</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>נתלי – באמא שך</v>
+        <v>ליאל שרעבי - לא סופרת</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שיר אוחנה - המילים שרציתי לכתוב</v>
+        <v>כנסיית השכל ואיתן רייטר – השיר מהגן</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411012&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
+        <v>https://yosmusic.com/%d7%9b%d7%a0%d7%a1%d7%99%d7%99%d7%aa-%d7%94%d7%a9%d7%9b%d7%9c-%d7%95%d7%90%d7%99%d7%aa%d7%9f-%d7%a8%d7%99%d7%99%d7%98%d7%a8-%d7%94%d7%a9%d7%99%d7%a8-%d7%9e%d7%94%d7%92%d7%9f/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>הרמיקס ל־“שיר מהגן” מצליח לקחת את הרגש הנוסטלגי והחשוף של כנסיית השכל ולהעביר אותו דרך פילטר אלקטרוני מהפנט של איתן רייטר – בלי לאבד את הלב של השיר. הטקסט  נשען על זיכרון חלקי, כמעט שבור:הדובר לא זוכר “את השיר מהגן”,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,202 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שיר אוחנה - המילים שרציתי לכתוב</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שי אוחיון - אלקנה</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411011&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שי אוחיון - אלקנה</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>קורל - בלילות</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411010&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>קורל - בלילות</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נתנאל פורטל - כפרה</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411009&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נתנאל פורטל - כפרה</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מוטי אוריאל - עם סגולה</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411008&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מוטי אוריאל - עם סגולה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>ליאל שרעבי - לא סופרת</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411007&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>ליאל שרעבי - לא סופרת</v>
+        <v>כנסיית השכל ואיתן רייטר – השיר מהגן</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>כנסיית השכל ואיתן רייטר – השיר מהגן</v>
+        <v>אביעד סהר - הילד שביקשתי קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9b%d7%a0%d7%a1%d7%99%d7%99%d7%aa-%d7%94%d7%a9%d7%9b%d7%9c-%d7%95%d7%90%d7%99%d7%aa%d7%9f-%d7%a8%d7%99%d7%99%d7%98%d7%a8-%d7%94%d7%a9%d7%99%d7%a8-%d7%9e%d7%94%d7%92%d7%9f/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=394212&amp;sid=c5c5533b3b28611bd1aaa0c50db5f783</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-25</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הרמיקס ל־“שיר מהגן” מצליח לקחת את הרגש הנוסטלגי והחשוף של כנסיית השכל ולהעביר אותו דרך פילטר אלקטרוני מהפנט של איתן רייטר – בלי לאבד את הלב של השיר. הטקסט  נשען על זיכרון חלקי, כמעט שבור:הדובר לא זוכר “את השיר מהגן”,</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>כנסיית השכל ואיתן רייטר – השיר מהגן</v>
+        <v>אביעד סהר - הילד שביקשתי קאבר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אביעד סהר - הילד שביקשתי קאבר</v>
+        <v>ליאור יונה - מטורף בלילות &amp; השיר האחרון</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=394212&amp;sid=c5c5533b3b28611bd1aaa0c50db5f783</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411026&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-25</v>
@@ -469,12 +469,506 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אביעד סהר - הילד שביקשתי קאבר</v>
+        <v>ליאור יונה - מטורף בלילות &amp; השיר האחרון</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>יונתן סבה - מחרוזת אדון עולם 2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411025&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>יונתן סבה - מחרוזת אדון עולם 2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>יובל גיגי - בשבילי נברא העולם</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411024&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>יובל גיגי - בשבילי נברא העולם</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>טודיאל - אל תפחד</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411023&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>טודיאל - אל תפחד</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>חגי מולה - לא מלאך</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411022&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>חגי מולה - לא מלאך</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>השקוף - מודה אני</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411021&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>השקוף - מודה אני</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>הראל סבג - בשמלה ירוקה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411020&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>הראל סבג - בשמלה ירוקה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>הילה וקנין - מי היה שם באמת</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411019&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>הילה וקנין - מי היה שם באמת</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>דדי מזרחי - הודעה קטנה ממך</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411018&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>דדי מזרחי - הודעה קטנה ממך</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אסף בר נתן - לעולם לא שלי</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411017&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אסף בר נתן - לעולם לא שלי</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אוריה אזערי - לא חוזר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411016&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אוריה אזערי - לא חוזר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אודי דמארי - כולנו יחד</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411015&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אודי דמארי - כולנו יחד</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אביעד - מי אמר</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411014&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אביעד - מי אמר</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אבי סינואני - כולם יודעים קאבר</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411013&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אבי סינואני - כולם יודעים קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליאור יונה - מטורף בלילות &amp; השיר האחרון</v>
+        <v>שלומי ימין - כלה שלי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411026&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411033&amp;sid=55a05d73587d1c30271d40149943d46a</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-25</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליאור יונה - מטורף בלילות &amp; השיר האחרון</v>
+        <v>שלומי ימין - כלה שלי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יונתן סבה - מחרוזת אדון עולם 2026</v>
+        <v>קורין גמליאל - עם היופי שלי והשכל שלך</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411025&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411032&amp;sid=55a05d73587d1c30271d40149943d46a</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-25</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יונתן סבה - מחרוזת אדון עולם 2026</v>
+        <v>קורין גמליאל - עם היופי שלי והשכל שלך</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יובל גיגי - בשבילי נברא העולם</v>
+        <v>עודד מנשרי - טוב ועוד טוב</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411024&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411031&amp;sid=55a05d73587d1c30271d40149943d46a</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-25</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יובל גיגי - בשבילי נברא העולם</v>
+        <v>עודד מנשרי - טוב ועוד טוב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>טודיאל - אל תפחד</v>
+        <v>עדן מאירי - לב לבן קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411023&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411030&amp;sid=55a05d73587d1c30271d40149943d46a</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-25</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>טודיאל - אל תפחד</v>
+        <v>עדן מאירי - לב לבן קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>חגי מולה - לא מלאך</v>
+        <v>נרקיס - שעת רצון</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411022&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411029&amp;sid=55a05d73587d1c30271d40149943d46a</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-25</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>חגי מולה - לא מלאך</v>
+        <v>נרקיס - שעת רצון</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>השקוף - מודה אני</v>
+        <v>ליעד בנאי - צחוק של ילדים</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411021&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411028&amp;sid=55a05d73587d1c30271d40149943d46a</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-25</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>השקוף - מודה אני</v>
+        <v>ליעד בנאי - צחוק של ילדים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>הראל סבג - בשמלה ירוקה</v>
+        <v>ליאם גולן - אוהב או שונא</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411020&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411027&amp;sid=55a05d73587d1c30271d40149943d46a</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-25</v>
@@ -697,278 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>הראל סבג - בשמלה ירוקה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>הילה וקנין - מי היה שם באמת</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411019&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>הילה וקנין - מי היה שם באמת</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>דדי מזרחי - הודעה קטנה ממך</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411018&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>דדי מזרחי - הודעה קטנה ממך</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אסף בר נתן - לעולם לא שלי</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411017&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אסף בר נתן - לעולם לא שלי</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אוריה אזערי - לא חוזר</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411016&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אוריה אזערי - לא חוזר</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אודי דמארי - כולנו יחד</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411015&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אודי דמארי - כולנו יחד</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אביעד - מי אמר</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411014&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אביעד - מי אמר</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>אבי סינואני - כולם יודעים קאבר</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411013&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>אבי סינואני - כולם יודעים קאבר</v>
+        <v>ליאם גולן - אוהב או שונא</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי ימין - כלה שלי</v>
+        <v>עמרם אדר - מברוק</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411033&amp;sid=55a05d73587d1c30271d40149943d46a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411045&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי ימין - כלה שלי</v>
+        <v>עמרם אדר - מברוק</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קורין גמליאל - עם היופי שלי והשכל שלך</v>
+        <v>מיכל לבייב - אורזת מזוודה - לנשים בלבד</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411032&amp;sid=55a05d73587d1c30271d40149943d46a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411044&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קורין גמליאל - עם היופי שלי והשכל שלך</v>
+        <v>מיכל לבייב - אורזת מזוודה - לנשים בלבד</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עודד מנשרי - טוב ועוד טוב</v>
+        <v>ליאורה יצחק - רואה אותי</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411031&amp;sid=55a05d73587d1c30271d40149943d46a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411043&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עודד מנשרי - טוב ועוד טוב</v>
+        <v>ליאורה יצחק - רואה אותי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עדן מאירי - לב לבן קאבר</v>
+        <v>יונתן שחר - שום דבר בעולם</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411030&amp;sid=55a05d73587d1c30271d40149943d46a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411042&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עדן מאירי - לב לבן קאבר</v>
+        <v>יונתן שחר - שום דבר בעולם</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נרקיס - שעת רצון</v>
+        <v>טוני ג'ינו - עלילה</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411029&amp;sid=55a05d73587d1c30271d40149943d46a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411041&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נרקיס - שעת רצון</v>
+        <v>טוני ג'ינו - עלילה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ליעד בנאי - צחוק של ילדים</v>
+        <v>אריאל זילבר - תנו לשמש להפציע (זה יבוא וזה יגיע)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411028&amp;sid=55a05d73587d1c30271d40149943d46a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411040&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ליעד בנאי - צחוק של ילדים</v>
+        <v>אריאל זילבר - תנו לשמש להפציע (זה יבוא וזה יגיע)</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ליאם גולן - אוהב או שונא</v>
+        <v>איתן כהן - אבא</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411027&amp;sid=55a05d73587d1c30271d40149943d46a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411039&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,12 +697,240 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ליאם גולן - אוהב או שונא</v>
+        <v>איתן כהן - אבא</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>איילת בוקר - אור השם</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411038&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>איילת בוקר - אור השם</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אוראל דהרי - לב קרוע</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411037&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אוראל דהרי - לב קרוע</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אור קודאי - את לא יודעת</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411036&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אור קודאי - את לא יודעת</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אדיר גץ - לפרוטוקול</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411035&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אדיר גץ - לפרוטוקול</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אדיר גץ - לחצן מצוקה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411034&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אדיר גץ - לחצן מצוקה</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>נרקיס – שעת רצון</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="C14" t="str">
+        <v>https://yosmusic.com/%d7%a0%d7%a8%d7%a7%d7%99%d7%a1-%d7%a9%d7%a2%d7%aa-%d7%a8%d7%a6%d7%95%d7%9f/</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>"שעת רצון” של נרקיס מנסה להיות הרבה יותר משיר אהבה: הוא מבקש לתפקד כמעט כתפילה פופולרית־רוחנית. זה שיר על תיקון, אמונה, ריפוי זוגי ופנימי, האפשרות “להחזיר אור” בתוך מציאות שבורה. אבל בדיוק בנקודה הזאת נמצאת גם החולשה הגדולה שלו. יש</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>נרקיס – שעת רצון</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עמרם אדר - מברוק</v>
+        <v>ישראל ורולקר - ירושלים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411045&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411054&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-26</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עמרם אדר - מברוק</v>
+        <v>ישראל ורולקר - ירושלים</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מיכל לבייב - אורזת מזוודה - לנשים בלבד</v>
+        <v>יוסי שטרית - ילד טוב</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411044&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411053&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-26</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מיכל לבייב - אורזת מזוודה - לנשים בלבד</v>
+        <v>יוסי שטרית - ילד טוב</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאורה יצחק - רואה אותי</v>
+        <v>טודיאל - מתמודד עם הפחד</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411043&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411052&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-26</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאורה יצחק - רואה אותי</v>
+        <v>טודיאל - מתמודד עם הפחד</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יונתן שחר - שום דבר בעולם</v>
+        <v>טודיאל - לפרוק</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411042&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411051&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-26</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יונתן שחר - שום דבר בעולם</v>
+        <v>טודיאל - לפרוק</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>טוני ג'ינו - עלילה</v>
+        <v>דודא - געגועים</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411041&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411050&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-26</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>טוני ג'ינו - עלילה</v>
+        <v>דודא - געגועים</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אריאל זילבר - תנו לשמש להפציע (זה יבוא וזה יגיע)</v>
+        <v>אריאל בורסוצקי - לראות רק טוב</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411040&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411049&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-26</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אריאל זילבר - תנו לשמש להפציע (זה יבוא וזה יגיע)</v>
+        <v>אריאל בורסוצקי - לראות רק טוב</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>איתן כהן - אבא</v>
+        <v>אליה אבוקרט - תלך</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411039&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411048&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-26</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>איתן כהן - אבא</v>
+        <v>אליה אבוקרט - תלך</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>איילת בוקר - אור השם</v>
+        <v>אברהם יצחק - תבוא אליי</v>
       </c>
       <c r="B9" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411038&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411047&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-26</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>איילת בוקר - אור השם</v>
+        <v>אברהם יצחק - תבוא אליי</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אוראל דהרי - לב קרוע</v>
+        <v>אבירם פרחן - מאשאפ רק את &amp; אם את עוד אוהבת</v>
       </c>
       <c r="B10" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411037&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411046&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-26</v>
@@ -773,164 +773,12 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אוראל דהרי - לב קרוע</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אור קודאי - את לא יודעת</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411036&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אור קודאי - את לא יודעת</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אדיר גץ - לפרוטוקול</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411035&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אדיר גץ - לפרוטוקול</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אדיר גץ - לחצן מצוקה</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411034&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אדיר גץ - לחצן מצוקה</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>נרקיס – שעת רצון</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C14" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%a8%d7%a7%d7%99%d7%a1-%d7%a9%d7%a2%d7%aa-%d7%a8%d7%a6%d7%95%d7%9f/</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v>"שעת רצון” של נרקיס מנסה להיות הרבה יותר משיר אהבה: הוא מבקש לתפקד כמעט כתפילה פופולרית־רוחנית. זה שיר על תיקון, אמונה, ריפוי זוגי ופנימי, האפשרות “להחזיר אור” בתוך מציאות שבורה. אבל בדיוק בנקודה הזאת נמצאת גם החולשה הגדולה שלו. יש</v>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>נרקיס – שעת רצון</v>
+        <v>אבירם פרחן - מאשאפ רק את &amp; אם את עוד אוהבת</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ישראל ורולקר - ירושלים</v>
+        <v>דניאל וייס – מכור</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411054&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
+        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c-%d7%95%d7%99%d7%99%d7%a1-%d7%9e%d7%9b%d7%95%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>דניאל וייס שר על החיים בתוך תרבות של עודף – עוד גירויים, עוד רעש, עוד בריחה.זה שיר שלא מדבר על התמכרות קיצונית, אלא על ההתמכרויות המתפקדות, היומיומיות, שכבר נטמעו בתוך שגרת החיים המודרנית עד שהן נראות נורמליות לגמרי. הוא לא</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,316 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ישראל ורולקר - ירושלים</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>יוסי שטרית - ילד טוב</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411053&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>יוסי שטרית - ילד טוב</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>טודיאל - מתמודד עם הפחד</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411052&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>טודיאל - מתמודד עם הפחד</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>טודיאל - לפרוק</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411051&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>טודיאל - לפרוק</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>דודא - געגועים</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411050&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>דודא - געגועים</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אריאל בורסוצקי - לראות רק טוב</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411049&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אריאל בורסוצקי - לראות רק טוב</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אליה אבוקרט - תלך</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411048&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אליה אבוקרט - תלך</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אברהם יצחק - תבוא אליי</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411047&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אברהם יצחק - תבוא אליי</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אבירם פרחן - מאשאפ רק את &amp; אם את עוד אוהבת</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411046&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אבירם פרחן - מאשאפ רק את &amp; אם את עוד אוהבת</v>
+        <v>דניאל וייס – מכור</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דניאל וייס – מכור</v>
+        <v>שלמה בר מארח את אהוד בנאי – צור משלו אכלנו</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c-%d7%95%d7%99%d7%99%d7%a1-%d7%9e%d7%9b%d7%95%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%91%d7%a8-%d7%9e%d7%90%d7%a8%d7%97-%d7%90%d7%aa-%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%a6%d7%95%d7%a8-%d7%9e%d7%a9%d7%9c%d7%95-%d7%90%d7%9b%d7%9c%d7%a0%d7%95/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-27</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>דניאל וייס שר על החיים בתוך תרבות של עודף – עוד גירויים, עוד רעש, עוד בריחה.זה שיר שלא מדבר על התמכרות קיצונית, אלא על ההתמכרויות המתפקדות, היומיומיות, שכבר נטמעו בתוך שגרת החיים המודרנית עד שהן נראות נורמליות לגמרי. הוא לא</v>
+        <v>הגרסה החדשה של "צור משלו אכלנו” של שלמה בר יחד עם אהוד בנאי היא הרבה מעבר לעיבוד מחודש לפיוט מוכר. זהו מפגש בין שתי תפיסות רוחניות־מוזיקליות של המוזיקה הישראלית- הטקסיות השבטית־מרוקאית של שלמה בר מול רוח הנדודים העירוניים־המדבריים של אהוד</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דניאל וייס – מכור</v>
+        <v>שלמה בר מארח את אהוד בנאי – צור משלו אכלנו</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלמה בר מארח את אהוד בנאי – צור משלו אכלנו</v>
+        <v>שי בן לוי - מנהרת הזמן</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%91%d7%a8-%d7%9e%d7%90%d7%a8%d7%97-%d7%90%d7%aa-%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%a6%d7%95%d7%a8-%d7%9e%d7%a9%d7%9c%d7%95-%d7%90%d7%9b%d7%9c%d7%a0%d7%95/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411071&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-27</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הגרסה החדשה של "צור משלו אכלנו” של שלמה בר יחד עם אהוד בנאי היא הרבה מעבר לעיבוד מחודש לפיוט מוכר. זהו מפגש בין שתי תפיסות רוחניות־מוזיקליות של המוזיקה הישראלית- הטקסיות השבטית־מרוקאית של שלמה בר מול רוח הנדודים העירוניים־המדבריים של אהוד</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,620 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלמה בר מארח את אהוד בנאי – צור משלו אכלנו</v>
+        <v>שי בן לוי - מנהרת הזמן</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>עמית מור - משקר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411070&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>עמית מור - משקר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>לילך בטאט - בת מלך</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411069&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>לילך בטאט - בת מלך</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>בר צברי - ככה באמת</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411068&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>בר צברי - ככה באמת</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אליאור שמש - נעימת השיכורות</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411067&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אליאור שמש - נעימת השיכורות</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אילן יעקב - האור שבך</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411066&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אילן יעקב - האור שבך</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>שלמה בר מארח את אהוד בנאי - צור משלו אכלנו</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411065&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>שלמה בר מארח את אהוד בנאי - צור משלו אכלנו</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>שלומי ימין - געגועים</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411064&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>שלומי ימין - געגועים</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>שילה בן סעדון - חולה אהבה</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411063&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>שילה בן סעדון - חולה אהבה</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>קורל ראובן - לפניך</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411062&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>קורל ראובן - לפניך</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>סתיו שמש - היופי שבאמצע</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411061&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>סתיו שמש - היופי שבאמצע</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>מיתר רובין - פרחי אהבה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411060&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>מיתר רובין - פרחי אהבה</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>מיקי אוזן - הנגב בוער - שיר האליפות הפועל באר שבע 2025-2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411059&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>מיקי אוזן - הנגב בוער - שיר האליפות הפועל באר שבע 2025-2026</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>מיכאל חן - למה אני חי</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411058&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>מיכאל חן - למה אני חי</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>מיכאל בן שבת - סיגריה בחלון</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411057&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>מיכאל בן שבת - סיגריה בחלון</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>יניב מדר - דרך ארוכה</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411056&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>יניב מדר - דרך ארוכה</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>גל שלום - המלכה והמשורר</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411055&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>גל שלום - המלכה והמשורר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בר צברי – ככה באמת</v>
+        <v>עופר סופר - עזר כנגדי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-28</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%a8-%d7%a6%d7%91%d7%a8%d7%99-%d7%9b%d7%9b%d7%94-%d7%91%d7%90%d7%9e%d7%aa/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411085&amp;sid=b422efd5031a5485d41e23a8d861d86c</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-28</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>בר צברי שר שיר אהבה שמצליח לגעת דווקא בגלל הפשטות שלו. הוא לא מנסה להיות פיוטי מדי, מתוחכם מדי או דרמטי מדי  אלא נשען על דיבור ישיר, כמעט יומיומי, שמבקש לומר דבר אחד פשוט: אהבה אמיתית נבנית מהחיים עצמם, וזה</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בר צברי – ככה באמת</v>
+        <v>עופר סופר - עזר כנגדי</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>עופר סופר - אשת חיל</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411084&amp;sid=b422efd5031a5485d41e23a8d861d86c</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>עופר סופר - אשת חיל</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>משה הלל - אור הגאולה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411083&amp;sid=b422efd5031a5485d41e23a8d861d86c</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>משה הלל - אור הגאולה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>